--- a/artfynd/A 43074-2022 artfynd.xlsx
+++ b/artfynd/A 43074-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43074-2022 artfynd.xlsx
+++ b/artfynd/A 43074-2022 artfynd.xlsx
@@ -1067,10 +1067,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119645823</v>
+        <v>119646005</v>
       </c>
       <c r="B5" t="n">
-        <v>58013</v>
+        <v>57738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721199</v>
+        <v>721139</v>
       </c>
       <c r="R5" t="n">
-        <v>6396191</v>
+        <v>6396117</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,10 +1169,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119646005</v>
+        <v>119645823</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>58013</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,21 +1185,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>103055</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721139</v>
+        <v>721199</v>
       </c>
       <c r="R6" t="n">
-        <v>6396117</v>
+        <v>6396191</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 43074-2022 artfynd.xlsx
+++ b/artfynd/A 43074-2022 artfynd.xlsx
@@ -1067,10 +1067,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119646005</v>
+        <v>119645823</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>58013</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>721139</v>
+        <v>721199</v>
       </c>
       <c r="R5" t="n">
-        <v>6396117</v>
+        <v>6396191</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,10 +1169,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119645823</v>
+        <v>119646005</v>
       </c>
       <c r="B6" t="n">
-        <v>58013</v>
+        <v>57738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,21 +1185,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>103001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>721199</v>
+        <v>721139</v>
       </c>
       <c r="R6" t="n">
-        <v>6396191</v>
+        <v>6396117</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 43074-2022 artfynd.xlsx
+++ b/artfynd/A 43074-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1269,6 +1269,108 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124031259</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58196</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>721210</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6396181</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bäl</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Leif Lithander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Leif Lithander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
